--- a/config/recharges.xlsx
+++ b/config/recharges.xlsx
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>月パス(小)</t>
+          <t>月票（小）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>連続30日で毎日100ダイヤを受け取る</t>
+          <t>连续30天每天领取100颗钻石</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
-          <t>連続30日で毎日100ダイヤを受け取る</t>
+          <t>连续30天每天领取100颗钻石</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>月パス(大)</t>
+          <t>月球通行证（大）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>連続30日で毎日150ダイヤを受け取る</t>
+          <t>连续30天每天可获得150颗钻石</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB5" s="7" t="inlineStr">
         <is>
-          <t>連続30日で毎日150ダイヤを受け取る</t>
+          <t>连续30天每天可获得150颗钻石</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>6480ダイヤ</t>
+          <t>6480颗钻石</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>別途6480ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送6480钻石（仅第一次）</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>3280ダイヤ</t>
+          <t>3280颗钻石</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>別途3280ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送3280颗钻石（仅第一次）</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1980ダイヤ</t>
+          <t>1980年钻石</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="V8" s="7" t="inlineStr">
         <is>
-          <t>別途1980ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送1980钻石（仅第一次）</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>980ダイヤ</t>
+          <t>980颗钻石</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>別途980ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送980钻石（仅第一次）</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>600ダイヤ</t>
+          <t>600颗钻石</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>別途600ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送600钻石（仅限第一次）</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>300ダイヤ</t>
+          <t>300颗钻石</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="V11" s="7" t="inlineStr">
         <is>
-          <t>別途300ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送300钻石（仅第一次）</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>60ダイヤ</t>
+          <t>60颗钻石</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="V12" s="7" t="inlineStr">
         <is>
-          <t>別途60ダイヤをプレゼント(初回のみ)</t>
+          <t>另外赠送60钻石（仅第一次）</t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>特価パック1</t>
+          <t>特价套餐1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>特価パック6</t>
+          <t>特价包6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>特価パック12</t>
+          <t>特价包12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>特価パック18</t>
+          <t>特价套餐18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>特価パック25</t>
+          <t>特价包装25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>特価パック30</t>
+          <t>特价包30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>特価パック60</t>
+          <t>特价包装60</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>特価パック98</t>
+          <t>特价套餐98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>特価パック128</t>
+          <t>特价包128</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>特価パック168</t>
+          <t>特价包168</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>特価パック198</t>
+          <t>特价套餐198</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>特価パック328</t>
+          <t>特价包328</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>特価パック648</t>
+          <t>特价套餐648</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>特価パック825</t>
+          <t>特价包装825</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>特価パック1100</t>
+          <t>特价套餐1100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>特価パック1800</t>
+          <t>特价包1800</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>特価パック88</t>
+          <t>特价包88</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>特価パック188</t>
+          <t>特价套餐188</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>特価パック288</t>
+          <t>特价套餐288</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>推送パック（一键打包购买1960日元）-98</t>
+          <t>推送包（一键打包购买1960天）-98</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>推送パック（一键打包购买3900日元）-198</t>
+          <t>推送包（一键打包购买3900天）-198</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>推送パック（一键打包购买6500日元）-328</t>
+          <t>推送包（一键打包购买6500天）-328</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>推送パック（一键打包购买12800日元）-648</t>
+          <t>推送包（一键打包购买12800天）-648</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>推送パック（一键打包购买3300日元）</t>
+          <t>推送包（一键打包购买3300天）</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
